--- a/pacjenci/ROMAN SŁOTA.xlsx
+++ b/pacjenci/ROMAN SŁOTA.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ROMAN SŁOTA.xlsx
+++ b/pacjenci/ROMAN SŁOTA.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>14.04.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza - ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Pobudzone metabolicznie węzły chłonne szyjne grup 1B obustronnie wielkości do 20x14 mm SUV max do 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Liczne drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe po stronie prawej wielkości do 27x14 mm SUV max do 3,2; - międzypiersiowe i pachowe po stronie lewej wielkości do 24x8 mm SUV max do 3,2; - śródpiersiowe najwyższe wielkości do 13 mm SUV max do 2,8; - przytchawicze górne i dolne prawe wielkości do 41x23x30 mm SUV max do 5,0; - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 51x37x43 mm SUV max do 5,5 - podostrogowe wielkości do 56x48x78 mm wg PET SUV max do 5,6; - we wnęce płuca prawego SUV max do 3,3; - we wnęce płuca lewego SUV max do 3,2.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne i pobudzone metaboliczne węzły chłonne: - we wnęce wątroby, wielkości do 32x20 mm SUV max do 4,3; - okołoaortalne prawe wielkości do 52x33x82 mm SUV max do 4,6 - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 17 mm SUV max do 3,6; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 18 mm SUV max do 3,3. Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 11,1- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Niejednorodny metabolizm FDG w wątrobie i w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalne lewe wielkości do 15x11mm. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie, licznych grup węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>22.08.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Stan po 2 cyklach immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,2- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne  przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm SUV max do 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - pachowe obustronnie wielkości do 12 mm. - przytchawicze dolne prawe wielkości do 22x10 mm - podostrogowe wielkości do 20x15 mm.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,7- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20x16 mm - przyaortalne prawe wielkości do 10mm. - przyaortalne lewe wielkości do 11x 5mm - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13 mm  - przy naczyniach biodrowych zewnętrznych lewych wielkości do 10 mm   Układ kostny: Nieznacznie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,3- w pierwszej kolejności wynikający z stosowanego leczenia. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Wartości referencyjne: MBPS SUVmax 2,4 Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej- dobra odpowiedź metaboliczna choroby na stosowane leczenie z częściową regresją zmian radiologicznych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>01.12.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena remisji choroby przed autoPBSCT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm; - pachowe obustronnie wielkości do 12 mm; - przytchawicze dolne prawe wielkości do 19 mm; - podostrogowe wielkości do 15 mm.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,6 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 8mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 10mm.  Układ kostny: Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.    Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy resztkowe do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>10.6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>01.06.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 91 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,0- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej oraz w stropie tej zatoki.. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 5mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 23 mm; - przytchawicze dolne prawe wielkości do 26 mm; - podostrogowe wielkości do 31 mm. Płyn w jamie opłucnowej po stronie prawej o szerokości płaszcza do 21mm, a po lewej do 12mm.  Zwiększona ilość płynu w worku osierdziowym o szerokości do 39mm!  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 17,1 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Miernie powiększona prostata. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 9mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 9mm.  Układ kostny: Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.    Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy resztkowe do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>17.1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ROMAN SŁOTA.xlsx
+++ b/pacjenci/ROMAN SŁOTA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Pobudzone metabolicznie węzły chłonne szyjne grup 1B obustronnie wielkości do 20x14 mm SUV max do 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Liczne drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe po stronie prawej wielkości do 27x14 mm SUV max do 3,2; - międzypiersiowe i pachowe po stronie lewej wielkości do 24x8 mm SUV max do 3,2; - śródpiersiowe najwyższe wielkości do 13 mm SUV max do 2,8; - przytchawicze górne i dolne prawe wielkości do 41x23x30 mm SUV max do 5,0; - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 51x37x43 mm SUV max do 5,5 - podostrogowe wielkości do 56x48x78 mm wg PET SUV max do 5,6; - we wnęce płuca prawego SUV max do 3,3; - we wnęce płuca lewego SUV max do 3,2.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne i pobudzone metaboliczne węzły chłonne: - we wnęce wątroby, wielkości do 32x20 mm SUV max do 4,3; - okołoaortalne prawe wielkości do 52x33x82 mm SUV max do 4,6 - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 17 mm SUV max do 3,6; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 18 mm SUV max do 3,3. Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 11,1- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Niejednorodny metabolizm FDG w wątrobie i w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalne lewe wielkości do 15x11mm. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne szyjne grup 1B obustronnie wielkości do 20x14 mm SUV max do 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Liczne drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe po stronie prawej wielkości do 27x14 mm SUV max do 3,2; - międzypiersiowe i pachowe po stronie lewej wielkości do 24x8 mm SUV max do 3,2; - śródpiersiowe najwyższe wielkości do 13 mm SUV max do 2,8; - przytchawicze górne i dolne prawe wielkości do 41x23x30 mm SUV max do 5,0; - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 51x37x43 mm SUV max do 5,5 - podostrogowe wielkości do 56x48x78 mm wg PET SUV max do 5,6; - we wnęce płuca prawego SUV max do 3,3; - we wnęce płuca lewego SUV max do 3,2.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metaboliczne węzły chłonne: - we wnęce wątroby, wielkości do 32x20 mm SUV max do 4,3; - okołoaortalne prawe wielkości do 52x33x82 mm SUV max do 4,6 - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 17 mm SUV max do 3,6; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 18 mm SUV max do 3,3. Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 11,1- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Niejednorodny metabolizm FDG w wątrobie i w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalne lewe wielkości do 15x11mm. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie, licznych grup węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>11.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,2- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne  przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm SUV max do 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - pachowe obustronnie wielkości do 12 mm. - przytchawicze dolne prawe wielkości do 22x10 mm - podostrogowe wielkości do 20x15 mm.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,7- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20x16 mm - przyaortalne prawe wielkości do 10mm. - przyaortalne lewe wielkości do 11x 5mm - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13 mm  - przy naczyniach biodrowych zewnętrznych lewych wielkości do 10 mm   Układ kostny: Nieznacznie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,3- w pierwszej kolejności wynikający z stosowanego leczenia. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Wartości referencyjne: MBPS SUVmax 2,4 Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,2- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne  przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm SUV max do 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - pachowe obustronnie wielkości do 12 mm. - przytchawicze dolne prawe wielkości do 22x10 mm - podostrogowe wielkości do 20x15 mm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,7- wynikający w pierwszej kolejności ze stosowanego biguanidu - do ew. kontroli w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20x16 mm - przyaortalne prawe wielkości do 10mm. - przyaortalne lewe wielkości do 11x 5mm - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13 mm  - przy naczyniach biodrowych zewnętrznych lewych wielkości do 10 mm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nieznacznie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,3- w pierwszej kolejności wynikający z stosowanego leczenia. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej- dobra odpowiedź metaboliczna choroby na stosowane leczenie z częściową regresją zmian radiologicznych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm; - pachowe obustronnie wielkości do 12 mm; - przytchawicze dolne prawe wielkości do 19 mm; - podostrogowe wielkości do 15 mm.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,6 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 8mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 10mm.  Układ kostny: Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.    Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 7mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 19x15 mm; - pachowe obustronnie wielkości do 12 mm; - przytchawicze dolne prawe wielkości do 19 mm; - podostrogowe wielkości do 15 mm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 10,6 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 8mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 10mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy resztkowe do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>10.6</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 91 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,0- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej oraz w stropie tej zatoki.. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 5mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 23 mm; - przytchawicze dolne prawe wielkości do 26 mm; - podostrogowe wielkości do 31 mm. Płyn w jamie opłucnowej po stronie prawej o szerokości płaszcza do 21mm, a po lewej do 12mm.  Zwiększona ilość płynu w worku osierdziowym o szerokości do 39mm!  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 17,1 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Miernie powiększona prostata. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 9mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 9mm.  Układ kostny: Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.    Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG  na tylnej ścianie krtaniowej części gardła SUV max 7,0- odczynowo?- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej oraz w stropie tej zatoki.. Pojedyncze, drobne węzły chłonne szyjne obustronnie. Obwodowo uwapniony guzek w lewym płacie tarczycy wielkości 20x18mm - wskazane wykonanie badania USG tarczycy oraz kontrola endokrynologiczna.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Ok. 5mm guzek w segm. 2 płuca prawego oraz w segmencie 4/5 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne: - przytchawicze dolne lewe i okna aortalno-płucnego wielkości do 23 mm; - przytchawicze dolne prawe wielkości do 26 mm; - podostrogowe wielkości do 31 mm. Płyn w jamie opłucnowej po stronie prawej o szerokości płaszcza do 21mm, a po lewej do 12mm.  Zwiększona ilość płynu w worku osierdziowym o szerokości do 39mm!</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w obrębie jelit SUV max do 17,1 - wynikający w pierwszej kolejności ze stosowanego biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o pozaciąganych pozapalnie obrysach. Miernie powiększona prostata. Ok. 9x10mm nieco nieregularne zwapnienie w prawym kanale pachwinowym, poniżej drugie, ok. 6mm. Węzły chłonne: - pomiędzy VCI a żyłą wrotną wielkości do 20mm; - przyaortalne obustronnie wielkości do 9mm; - przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie wielkości do 9mm.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Nasilone zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy resztkowe do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>17.1</v>
       </c>
     </row>
